--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842125</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129490058</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129490061</v>
       </c>
       <c r="B4" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129490063</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129490060</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129490065</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129490058</v>
       </c>
       <c r="B3" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129490061</v>
       </c>
       <c r="B4" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129490063</v>
       </c>
       <c r="B5" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129490060</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,57 +1237,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129490055</v>
+        <v>129490065</v>
       </c>
       <c r="B7" t="n">
-        <v>4779</v>
+        <v>91609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tvär-Ramsdal, Tvär-Ramsdal, Srm</t>
+          <t>Tvär-Ramsdal, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637994</v>
+        <v>637992</v>
       </c>
       <c r="R7" t="n">
-        <v>6515331</v>
+        <v>6515365</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,52 +1348,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129490065</v>
+        <v>129490055</v>
       </c>
       <c r="B8" t="n">
-        <v>91608</v>
+        <v>4779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tvär-Ramsdal, Srm</t>
+          <t>Tvär-Ramsdal, Tvär-Ramsdal, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637992</v>
+        <v>637994</v>
       </c>
       <c r="R8" t="n">
-        <v>6515365</v>
+        <v>6515331</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129490058</v>
       </c>
       <c r="B3" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129490061</v>
       </c>
       <c r="B4" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129490063</v>
       </c>
       <c r="B5" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129490060</v>
       </c>
       <c r="B6" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129490065</v>
       </c>
       <c r="B7" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Birgitta Hamstedt , Eva Grusell</t>
+          <t>Eva Grusell, Birgitta Hamstedt , Göran Ekström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129490058</v>
       </c>
       <c r="B3" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129490061</v>
       </c>
       <c r="B4" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129490063</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129490060</v>
       </c>
       <c r="B6" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129490065</v>
       </c>
       <c r="B7" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Grusell, Birgitta Hamstedt , Göran Ekström</t>
+          <t>Göran Ekström, Birgitta Hamstedt , Eva Grusell</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 46042-2025 artfynd.xlsx
+++ b/artfynd/A 46042-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129490058</v>
       </c>
       <c r="B3" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129490061</v>
       </c>
       <c r="B4" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129490063</v>
       </c>
       <c r="B5" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129490060</v>
       </c>
       <c r="B6" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129490065</v>
       </c>
       <c r="B7" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
